--- a/artfynd/A 27404-2020 artfynd.xlsx
+++ b/artfynd/A 27404-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27404-2020 artfynd.xlsx
+++ b/artfynd/A 27404-2020 artfynd.xlsx
@@ -1376,7 +1376,7 @@
         <v>85739790</v>
       </c>
       <c r="B8" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619969.9952547863</v>
+        <v>619970</v>
       </c>
       <c r="R8" t="n">
-        <v>6905456.10045286</v>
+        <v>6905456</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1451,19 +1451,9 @@
           <t>2020-05-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-05-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 27404-2020 artfynd.xlsx
+++ b/artfynd/A 27404-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2287,6 +2287,112 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125653570</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80073</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Häljum, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>619902</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6905413</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27404-2020 artfynd.xlsx
+++ b/artfynd/A 27404-2020 artfynd.xlsx
@@ -2292,12 +2292,7 @@
         <v>125653570</v>
       </c>
       <c r="B16" t="n">
-        <v>80073</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27404-2020 artfynd.xlsx
+++ b/artfynd/A 27404-2020 artfynd.xlsx
@@ -2292,7 +2292,7 @@
         <v>125653570</v>
       </c>
       <c r="B16" t="n">
-        <v>80115</v>
+        <v>80116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27404-2020 artfynd.xlsx
+++ b/artfynd/A 27404-2020 artfynd.xlsx
@@ -2292,7 +2292,7 @@
         <v>125653570</v>
       </c>
       <c r="B16" t="n">
-        <v>80116</v>
+        <v>80120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27404-2020 artfynd.xlsx
+++ b/artfynd/A 27404-2020 artfynd.xlsx
@@ -2292,7 +2292,7 @@
         <v>125653570</v>
       </c>
       <c r="B16" t="n">
-        <v>80120</v>
+        <v>80121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27404-2020 artfynd.xlsx
+++ b/artfynd/A 27404-2020 artfynd.xlsx
@@ -2292,7 +2292,7 @@
         <v>125653570</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>80125</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
